--- a/extenbooks/S1702_extenbook.xlsx
+++ b/extenbooks/S1702_extenbook.xlsx
@@ -1116,7 +1116,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -2075,11 +2075,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2102,76 +2102,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Personal Income Dist below $200k (Fig 17.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1702_research.json", "adequacy_report": "Technical/docs/chapters/CH17_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1702_DPR.md", "epr": "Technical/docs/series/S1702_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1702_load.py", "processor": "Technical/code/P02_processors/P02_S1702_construct.py", "validator": "Technical/code/V03_validators/V03_S1702_validate.py", "processed": "Technical/data/processed/S1702.parquet", "chopped_csv": "Technical/chopped/S1702.csv"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:56:16.880881+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1702_extenbook.xlsx
+++ b/extenbooks/S1702_extenbook.xlsx
@@ -1063,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A121"/>
+  <dimension ref="A1:A119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1102,373 +1102,369 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Series ID**: S1702</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Series ID**: S1702</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>## 1. Definition</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>## 1. Definition</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cross-sectional snapshot at Tax Year 2011: the cumulative probability from</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cross-sectional snapshot at Tax Year 2011: the cumulative probability from</t>
+          <t>above (survival function) of personal income (AGI), restricted to bins with</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>above (survival function) of personal income (AGI), restricted to bins with</t>
+          <t>midpoint below $200,000 (the bottom 97% of returns). Appears in Shaikh (2016)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>midpoint below $200,000 (the bottom 97% of returns). Appears in Shaikh (2016)</t>
+          <t>as **Figure 17.2** (p. 752), plotted on a log-linear scale to test for</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>as **Figure 17.2** (p. 752), plotted on a log-linear scale to test for</t>
+          <t>exponentiality.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>exponentiality.</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>## 2. Why it matters in Chapter 17</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>## 2. Why it matters in Chapter 17</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>The bottom 97% of the IRS 2011 personal income distribution is approximately</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The bottom 97% of the IRS 2011 personal income distribution is approximately</t>
+          <t>exponential — appears as a straight line on a log-linear plot. Combined with</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>exponential — appears as a straight line on a log-linear plot. Combined with</t>
+          <t>the Pareto top tail (S1703), this validates the EPTC two-class framework</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>the Pareto top tail (S1703), this validates the EPTC two-class framework</t>
+          <t>(Yakovenko et al.) and yields Shaikh's reported Gini of 0.492 (~0.50 = pure</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>(Yakovenko et al.) and yields Shaikh's reported Gini of 0.492 (~0.50 = pure</t>
+          <t>exponential).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>exponential).</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>## 3. Source</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>## 3. Source</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>| Subseries | Source |</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| Subseries | Source |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>| S1702-A | IRS Statistics of Income (SOI), Publication 1304 (Complete Report), Table 1.4, Tax Year 2011 |</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>| S1702-A | IRS Statistics of Income, Publication 1304 (Complete Report), Table 1.4, Tax Year 2011 |</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Local salvage copy: the published Chapter 17 appendix data tables (Shaikh 2016, Appendix 17.1).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Salvage: `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix17_USIRS2011.xlsx`.</t>
+          <t>URL: https://www.irs.gov/statistics/soi-tax-stats-individual-income-tax-returns-publication-1304-complete-report (verified 200 OK 2026-05-18).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>URL: https://www.irs.gov/statistics/soi-tax-stats-individual-income-tax-returns-publication-1304-complete-report (verified 200 OK 2026-05-18).</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>`composite`. From the IRS Table 1.4 long form (AGI bin -&gt; number_of_returns),</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>`composite`. From the IRS Table 1.4 long form (AGI bin -&gt; number_of_returns),</t>
+          <t>the workbook computes:</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>the workbook computes:</t>
+          <t>1. Bin midpoint (arithmetic) for each AGI range.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1. Bin midpoint (arithmetic) for each AGI range.</t>
+          <t>2. Frequency = n_returns_i / total.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2. Frequency = n_returns_i / total.</t>
+          <t>3. Cumulative frequency from below.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3. Cumulative frequency from below.</t>
+          <t>4. Cumulative frequency from above = 1 - (3).</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>4. Cumulative frequency from above = 1 - (3).</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S1702-A loads the column "Cumulative Frequency from Above" (column FPR017_C5).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S1702-A loads column "Cumulative Frequency from Above" (FPR017_C5 in CD2</t>
+          <t>This corrects an earlier replication whose reference values pointed to the</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>naming) — Phase-4-ratified correction from the CD2 reference values which</t>
+          <t>Frequency column (FPR017_C3).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>had pointed to the Frequency column (FPR017_C3).</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>## 5. Year coverage</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>`year_range = [2011, 2011]` — single tax year, cross-sectional.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>`year_range = [2011, 2011]` — single tax year, cross-sectional.</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>## 6. Units</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>`cumulative_probability_from_above_dimensionless`, plotted on a natural-log</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>`cumulative_probability_from_above_dimensionless`, plotted on a natural-log</t>
+          <t>y-axis vs bin midpoint in USD (arithmetic x-axis).</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>y-axis vs bin midpoint in USD (arithmetic x-axis).</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1. **Column-fix.** Use column F (FPR017_C5), not column D (frequency).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1. **Column-fix.** Use column F (FPR017_C5), not column D (frequency) — Phase</t>
+          <t>2. **Top open-ended bin '$10,000,000 or more'** has no midpoint in the</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 confirmed.</t>
+          <t xml:space="preserve">   spreadsheet and is dropped (handled in S1703 logic; S1702 filter naturally</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2. **Top open-ended bin '$10,000,000 or more'** has no midpoint in the</t>
+          <t xml:space="preserve">   excludes it since midpoint &lt; $200k threshold).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">   spreadsheet and is dropped (handled in S1703 logic; S1702 filter naturally</t>
+          <t>3. **No extension** — cross_sectional content_type; future tax years are</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">   excludes it since midpoint &lt; $200k threshold).</t>
+          <t xml:space="preserve">   separate series, not extensions.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>3. **No extension** — cross_sectional content_type; future tax years are</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">   separate series, not extensions.</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
@@ -1478,31 +1474,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>- Earlier replications used the identifier S103</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>- Book: p. 752 (figure), 900 (Appendix 17.1 method)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>- CD legacy: S103; CD2 legacy: S103</t>
+          <t>- Companion: S1703 (top tail, Pareto)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>- Book: p. 752 (figure), 900 (Appendix 17.1 method)</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>- Companion: S1703 (top tail, Pareto)</t>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
@@ -1512,133 +1508,133 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>Tolerance ±0.5% on cell-by-cell match against workbook column F. Achieved:</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MAE 0.0, max 0.0%, n=17. PASS. Spot-checks all match to 4 decimal</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tolerance ±0.5% on cell-by-cell match against workbook column F. Achieved:</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>MAE 0.0, max 0.0%, n=17. PASS. Phase 4 spot-checks all match to 4 decimal</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
           <t>places.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4">
+    <row r="82">
+      <c r="A82" s="4">
         <f>== EPR: S1702_EPR.md ===</f>
         <v/>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t># S1702 — Extension Provenance Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+    </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t># S1702 — Extension Provenance Record</t>
+          <t>**Construction**: `composite`</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>**Content type**: `cross_sectional`</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t>**Extension method**: `not_applicable_cross_sectional`</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>**Construction**: `composite`</t>
+          <t>**Status v1**: complete (no extension to perform)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>**Content type**: `cross_sectional`</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>**Extension method**: `not_applicable_cross_sectional`</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>**Status v1**: complete (no extension to perform)</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>## 1. Why this series cannot be extended</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>S1702 is a cross-sectional snapshot at a single tax year (2011). Under the</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>## 1. Why this series cannot be extended</t>
+          <t>rule that extensions apply only to time-series data, cross-sectional</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>snapshots are not extended — each subsequent IRS Statistics of Income (SOI)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S1702 is a cross-sectional snapshot at a single tax year (2011). Per</t>
+          <t>release (Publication 1304, Tax Year YYYY) is a separate series, not a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>anu-framework: "Extensions ONLY apply to time_series type." Cross-sectional</t>
+          <t>continuation.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>snapshots are not extended — each subsequent IRS SOI release (Publication</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1304 Tax Year YYYY) is a separate series, not a continuation.</t>
+          <t>## 2. Future-tax-year reconstruction (not an extension)</t>
         </is>
       </c>
     </row>
@@ -1648,38 +1644,38 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>## 2. Future-tax-year reconstruction (not an extension)</t>
+          <t>A user wishing to update Figure 17.2 to a more recent tax year would:</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1. Download IRS SOI Pub 1304 Table 1.4 for the desired year.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A user wishing to update Figure 17.2 to a more recent tax year would:</t>
+          <t>2. Apply the same bin-midpoint -&gt; frequency -&gt; cum-from-above pipeline.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1. Download IRS SOI Pub 1304 Table 1.4 for the desired year.</t>
+          <t>3. Register it as a separate cross-sectional series.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2. Apply the same bin-midpoint -&gt; frequency -&gt; cum-from-above pipeline.</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3. Register it as a separate cross-sectional series.</t>
+          <t>This is NOT an extension of S1702 and would be a new RSCD series.</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1685,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>This is NOT an extension of S1702 and would be a new RSCD series.</t>
+          <t>## 3. Source substitutions and forecast data</t>
         </is>
       </c>
     </row>
@@ -1699,31 +1695,31 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>## 3. No-Proxy / No-Synthetic</t>
+          <t>The IRS is itself the canonical authoritative source. No substitution</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>required. The open-ended $10M+ bin has no midpoint in the workbook and is</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>The IRS is itself the canonical authoritative source. No substitution</t>
+          <t>not imputed (no value invented).</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>required. The open-ended $10M+ bin has no midpoint in the workbook and is</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>not imputed — anti-synthetic.</t>
+          <t>## 4. Divergence from earlier replications</t>
         </is>
       </c>
     </row>
@@ -1733,31 +1729,21 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>## 4. CD2 divergence pre-disclosure</t>
+          <t>An earlier replication's S103 reference values were the Frequency column</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>(FPR017_C3), not the Cumulative-from-Above (FPR017_C5). This is corrected</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CD2's S103 reference_values were the Frequency column (FPR017_C3), not the</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Cumulative-from-Above (FPR017_C5). Phase 4 corrected; RSCD v1 uses column F</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>and matches to &lt;0.01%.</t>
+          <t>here; RSCD v1 uses column F and matches to &lt;0.01%.</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1923,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2060,7 +2046,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T23:12:04.887847+00:00</t>
+          <t>2026-07-02T06:20:40.552869+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1702_extenbook.xlsx
+++ b/extenbooks/S1702_extenbook.xlsx
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:20:40.552869+00:00</t>
+          <t>2026-07-11T03:44:23.932160+00:00</t>
         </is>
       </c>
     </row>
@@ -2061,11 +2061,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2088,6 +2088,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IRS_SOI_2011_PUB1304_TABLE_1_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "KB-verified: figure 17.2 caption and in-text passage (p.752) match; IRS SOI Publication 1304 Table 1.4 (2011) sourcing confirmed; $10M+ open bin dropped (anti-synthetic). Verbatim quotes match.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1702_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1702_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 17.2; column-fix applied (FPR017_C3 -&gt; FPR017_C5); $10M+ open bin dropped (anti-synthetic).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cumulative_probability_from_above_dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
